--- a/Unity/Assets/Config/Excel/HeroConfig@cs.xlsx
+++ b/Unity/Assets/Config/Excel/HeroConfig@cs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Unity_Project\RogueLike\Unity\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B61D716-AAB8-4B8F-8700-533B24A092C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{775539DA-DBFB-48BF-92DA-9C8A54172079}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="828" yWindow="4980" windowWidth="23040" windowHeight="12660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="27">
   <si>
     <t>Id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -113,10 +113,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Dictionary&lt;int, long&gt;</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1000:50000,1002:5000000,1011:45000</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -134,6 +130,14 @@
   </si>
   <si>
     <t>1000:55000,1002:5000000,1011:45000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dictionary&lt;string, long&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -499,6 +503,7 @@
   <sheetFormatPr defaultColWidth="15.77734375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="7" max="7" width="23.5546875" customWidth="1"/>
+    <col min="8" max="8" width="32.109375" customWidth="1"/>
     <col min="10" max="10" width="22.77734375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -518,7 +523,9 @@
       <c r="G3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="3"/>
+      <c r="H3" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
     </row>
@@ -538,7 +545,9 @@
       <c r="G4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H4" s="3"/>
+      <c r="H4" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
     </row>
@@ -558,7 +567,9 @@
       <c r="G5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H5" s="3"/>
+      <c r="H5" s="6" t="s">
+        <v>25</v>
+      </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
     </row>
@@ -578,6 +589,9 @@
       <c r="G6" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="H6" s="5" t="s">
+        <v>20</v>
+      </c>
       <c r="J6" s="2"/>
     </row>
     <row r="7" spans="3:10" x14ac:dyDescent="0.25">
@@ -596,6 +610,9 @@
       <c r="G7" s="2" t="s">
         <v>15</v>
       </c>
+      <c r="H7" s="5" t="s">
+        <v>21</v>
+      </c>
       <c r="J7" s="2"/>
     </row>
     <row r="8" spans="3:10" x14ac:dyDescent="0.25">
@@ -614,6 +631,9 @@
       <c r="G8" s="2" t="s">
         <v>16</v>
       </c>
+      <c r="H8" s="5" t="s">
+        <v>22</v>
+      </c>
       <c r="J8" s="2"/>
     </row>
     <row r="9" spans="3:10" x14ac:dyDescent="0.25">
@@ -632,6 +652,9 @@
       <c r="G9" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="H9" s="5" t="s">
+        <v>23</v>
+      </c>
       <c r="J9" s="2"/>
     </row>
     <row r="10" spans="3:10" x14ac:dyDescent="0.25">
@@ -649,6 +672,9 @@
       </c>
       <c r="G10" s="2" t="s">
         <v>18</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>24</v>
       </c>
       <c r="J10" s="2"/>
     </row>
@@ -661,7 +687,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6B0E0CF-ACF9-4F8A-806F-ED1C3C9B80FF}">
-  <dimension ref="C3:I10"/>
+  <dimension ref="C2:I10"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="12.21875" customWidth="1"/>
@@ -673,6 +699,14 @@
     <col min="9" max="9" width="12.21875" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="2" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
     <row r="3" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C3" s="4" t="s">
         <v>0</v>
@@ -704,7 +738,7 @@
         <v>5</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
@@ -717,7 +751,7 @@
         <v>1001</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="3:9" x14ac:dyDescent="0.25">
@@ -725,7 +759,7 @@
         <v>1002</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="3:9" x14ac:dyDescent="0.25">
@@ -733,7 +767,7 @@
         <v>1003</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="3:9" x14ac:dyDescent="0.25">
@@ -741,7 +775,7 @@
         <v>1004</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="3:9" x14ac:dyDescent="0.25">
@@ -749,7 +783,7 @@
         <v>1005</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
